--- a/songs/BeMine_v1/quelle/struktur.xlsx
+++ b/songs/BeMine_v1/quelle/struktur.xlsx
@@ -436,15 +436,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,6 +469,7 @@
       <c r="C2" s="2" t="n">
         <v>26</v>
       </c>
+      <c r="D2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -478,6 +480,7 @@
       <c r="C3" s="2" t="n">
         <v>126</v>
       </c>
+      <c r="D3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -488,6 +491,7 @@
       <c r="C4" s="2" t="n">
         <v>0.375</v>
       </c>
+      <c r="D4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -502,20 +506,25 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Effektidee</t>
+          <t>Effekt (füllt KI)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>Änderungswunsch</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>Energie 0-5</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>BPM pro Part</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>bisher (alter Code)</t>
         </is>
@@ -530,13 +539,19 @@
           <t>pause</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progBlack(5000, 5)   (Matrix: progScrollText("Be Mine by Kamrad", 20238, 75, getRandomColor(), 10))</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>progBlack(5000, 5)   (Matrix: progScrollText("Be Mine by Kamrad", 20238, 75, getRandomColor(), 10))</t>
         </is>
@@ -551,13 +566,19 @@
           <t>intro</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progBlingBlingColoring(15238, 10, 946)</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>progBlingBlingColoring(15238, 10, 946)</t>
         </is>
@@ -572,13 +593,19 @@
           <t>verse 1a</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progPalette(15238, 1, 12)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>progPalette(15238, 1, 12)</t>
         </is>
@@ -593,13 +620,19 @@
           <t>verse 1b</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progPalette(15238, 4, 14)</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>progPalette(15238, 4, 14)</t>
         </is>
@@ -614,13 +647,19 @@
           <t>you got me so high</t>
         </is>
       </c>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progRandomLines(13333, 16, 470, false)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(13333, 16, 470, false)</t>
         </is>
@@ -635,13 +674,19 @@
           <t>snareroll</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(1905, 6, 18)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(1905, 6, 18)</t>
         </is>
@@ -656,13 +701,19 @@
           <t>chorus 1</t>
         </is>
       </c>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFullColors(15238, 20, 470)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>progFullColors(15238, 20, 470)</t>
         </is>
@@ -677,13 +728,19 @@
           <t>uebergang</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progBlack(1905, 22)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>progBlack(1905, 22)</t>
         </is>
@@ -698,13 +755,19 @@
           <t>verse 2</t>
         </is>
       </c>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progMatrixHorizontal(15238, 24, 70, true)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>progMatrixHorizontal(15238, 24, 70, true)</t>
         </is>
@@ -719,13 +782,19 @@
           <t>im going crazy</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progWaterRipple(15238, 26, 50, true, true)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(15238, 26, 50, true, true)</t>
         </is>
@@ -740,13 +809,19 @@
           <t>you got me so high</t>
         </is>
       </c>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progRandomLines(13333, 28, 470, false)</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(13333, 28, 470, false)</t>
         </is>
@@ -761,13 +836,19 @@
           <t>snareroll</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(1905, 6, 30)</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(1905, 6, 30)</t>
         </is>
@@ -782,13 +863,19 @@
           <t>chorus 2</t>
         </is>
       </c>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFullColors(13333, 32, 474)</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>progFullColors(13333, 32, 474)</t>
         </is>
@@ -803,13 +890,19 @@
           <t>strobe</t>
         </is>
       </c>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(1905, 34, 120, 255, 255, 255)</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1905, 34, 120, 255, 255, 255)</t>
         </is>
@@ -824,13 +917,19 @@
           <t>chorus 3</t>
         </is>
       </c>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(15238, 2, 36, 1, 20, 946)</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(15238, 2, 36, 1, 20, 946)</t>
         </is>
@@ -850,10 +949,10 @@
           <t>10 sek. BLACK</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>0</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <f>$C$3</f>
         <v/>
       </c>

--- a/songs/BeMine_v1/quelle/struktur.xlsx
+++ b/songs/BeMine_v1/quelle/struktur.xlsx
@@ -534,7 +534,7 @@
     </row>
     <row r="6" ht="28.8" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
     </row>
     <row r="7" ht="43.2" customHeight="1">
       <c r="A7" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -588,7 +588,7 @@
     </row>
     <row r="8" ht="28.8" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
     </row>
     <row r="9" ht="28.8" customHeight="1">
       <c r="A9" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
     </row>
     <row r="10" ht="43.2" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
     </row>
     <row r="11" ht="28.8" customHeight="1">
       <c r="A11" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
     </row>
     <row r="12" ht="28.8" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
     </row>
     <row r="13" ht="28.8" customHeight="1">
       <c r="A13" s="4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
     </row>
     <row r="14" ht="28.8" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
     </row>
     <row r="15" ht="28.8" customHeight="1">
       <c r="A15" s="4" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
     </row>
     <row r="16" ht="43.2" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
     </row>
     <row r="17" ht="28.8" customHeight="1">
       <c r="A17" s="4" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
     </row>
     <row r="18" ht="28.8" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
     </row>
     <row r="19" ht="28.8" customHeight="1">
       <c r="A19" s="4" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
     </row>
     <row r="20" ht="43.2" customHeight="1">
       <c r="A20" s="4" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>

--- a/songs/BeMine_v1/quelle/struktur.xlsx
+++ b/songs/BeMine_v1/quelle/struktur.xlsx
@@ -438,16 +438,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,6 +473,7 @@
         <v>26</v>
       </c>
       <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -483,6 +485,7 @@
         <v>126</v>
       </c>
       <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -494,6 +497,7 @@
         <v>0.375</v>
       </c>
       <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -518,15 +522,20 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>Neuer Vorschlag (KI)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>Energie 0-5</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>BPM pro Part</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>bisher (alter Code)</t>
         </is>
@@ -548,12 +557,13 @@
         </is>
       </c>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>progBlack(5000, 5)   (Matrix: progScrollText("Be Mine by Kamrad", 20238, 75, getRandomColor(), 10))</t>
         </is>
@@ -575,12 +585,17 @@
         </is>
       </c>
       <c r="D7" s="6" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Szene Glow, SUNSET, weich eingeblendet (fade_in 4 Beats).</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>progBlingBlingColoring(15238, 10, 946)</t>
         </is>
@@ -602,12 +617,17 @@
         </is>
       </c>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Szene Verse, SUNSET: dezenter Puls im Beat (bisher Regenbogen-Streifen).</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>progPalette(15238, 1, 12)</t>
         </is>
@@ -629,12 +649,17 @@
         </is>
       </c>
       <c r="D9" s="6" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Szene Palette, SUNSET -&gt; Farbwanderung nach NEON (2 Takte): Farbband über die ganze Bühne.</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>progPalette(15238, 4, 14)</t>
         </is>
@@ -656,12 +681,17 @@
         </is>
       </c>
       <c r="D10" s="6" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Linien bleiben (stapeln sich), darüber baut sich ein Glitzern auf (Ebene Sparkle, fade_in über 7 Takte). Fester Look für beide.</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(13333, 16, 470, false)</t>
         </is>
@@ -683,12 +713,17 @@
         </is>
       </c>
       <c r="D11" s="6" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Szene Buildup (1 Takt), NEON: lädt sich auf, Explosion genau auf den Chorus - der Blinder des Users steht dann auf dem Einsatz.</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(1905, 6, 18)</t>
         </is>
@@ -715,12 +750,17 @@
           <t>starker blinder am Anfang!</t>
         </is>
       </c>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Szene Colors, NEON, soft 30 (feste Farben, kurze Blende); Blinder am Anfang bleibt. Auf der Matrix "BE MINE" über der Szene (2 Takte, blendet aus).</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>progFullColors(15238, 20, 470)</t>
         </is>
@@ -742,12 +782,17 @@
         </is>
       </c>
       <c r="D13" s="6" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Schwarz bleibt; in den letzten 2 Beats weich ins Verse (verse 2 mit Übergang fade).</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>progBlack(1905, 22)</t>
         </is>
@@ -769,12 +814,17 @@
         </is>
       </c>
       <c r="D14" s="6" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Leuchtspuren bleiben (Szene Rain, ROYAL) - kühler Kontrast zum Chorus.</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>progMatrixHorizontal(15238, 24, 70, true)</t>
         </is>
@@ -796,12 +846,17 @@
         </is>
       </c>
       <c r="D15" s="6" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Szene DNA Flip, NEON: stehende Helix auf der Matrix, alle anderen pulsieren einmal je Takt (bisher Wasserringe).</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(15238, 26, 50, true, true)</t>
         </is>
@@ -823,12 +878,13 @@
         </is>
       </c>
       <c r="D16" s="6" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(13333, 28, 470, false)</t>
         </is>
@@ -850,12 +906,17 @@
         </is>
       </c>
       <c r="D17" s="6" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>wie beim ersten Mal (Buildup).</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(1905, 6, 30)</t>
         </is>
@@ -877,12 +938,17 @@
         </is>
       </c>
       <c r="D18" s="6" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Colors wie chorus 1, Blinder auf den Einsatz, Lampen blitzen weiß auf 2 und 4.</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>progFullColors(13333, 32, 474)</t>
         </is>
@@ -904,12 +970,17 @@
         </is>
       </c>
       <c r="D19" s="6" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Starker Blinder statt Strobo: blendet 2 Beats ein und steht 2 Beats voll bis zum Einsatz von chorus 3.</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1905, 34, 120, 255, 255, 255)</t>
         </is>
@@ -936,12 +1007,17 @@
           <t>blinder am ende</t>
         </is>
       </c>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Anwachsende Einzelblitze bleiben, in FIRE; drei kurze Blinder Ende des 4. Takts (Takt 80,5 / 80,75 / 81). Der Blinder am Ende bleibt.</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(15238, 2, 36, 1, 20, 946)</t>
         </is>
@@ -961,10 +1037,10 @@
           <t>10 sek. BLACK</t>
         </is>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>0</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <f>$C$3</f>
         <v/>
       </c>

--- a/songs/BeMine_v1/quelle/struktur.xlsx
+++ b/songs/BeMine_v1/quelle/struktur.xlsx
@@ -552,7 +552,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>progBlack(5000, 5)
+          <t>progBlack(5000, 3)
 Alles schwarz bis zum Intro (die Matrix zeigt den Titel-Lauftext).</t>
         </is>
       </c>
@@ -580,7 +580,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>progBlingBlingColoring(15238, 10, 952)
+          <t>progBlingBlingColoring(15238, 4, 952)
 Alter Effekt: jedes Gerät füllt sich LED für LED mit einer Farbe, alle 2 Beats kommt die nächste.</t>
         </is>
       </c>
@@ -612,7 +612,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>progPalette(15238, 1, 15)
+          <t>progPalette(15238, 1, 5)
 Alter Effekt: Regenbogen-Streifen mit harten Kanten laufen über die Geräte.</t>
         </is>
       </c>
@@ -644,7 +644,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>progPalette(15238, 4, 20)
+          <t>progPalette(15238, 4, 6)
 Alter Effekt: bunte, unterschiedlich helle Farbflecken laufen weich über die Geräte.</t>
         </is>
       </c>
@@ -676,7 +676,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>progRandomLines(13334, 25, 476, false)
+          <t>progRandomLines(13334, 7, 476, false)
 Alter Effekt: pro Beat eine weitere zufällige Linie, die Linien bleiben stehen und füllen das Bild.</t>
         </is>
       </c>
@@ -708,7 +708,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>progFastBlingBling(1904, 6, 30)
+          <t>progFastBlingBling(1904, 6, 8)
 Alter Effekt: 1 Takt schnelle Einzelblitze als Auftakt zum Chorus.</t>
         </is>
       </c>
@@ -740,7 +740,7 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>progFullColors(15238, 35, 476)
+          <t>progFullColors(15238, 9, 476)
 Ausgabe: Blinder bei 0 ms, 1905 ms lang, Blinder blendet 0 ms ein, 952 ms voll, 953 ms aus
 Auf den Chorus-Einsatz springt ein starker Blinder auf (warmweiß, alle Geräte): 2 Beats voll hell, klingt über 2 Beats ab. Darunter der alte Effekt: alle LEDs einfarbig, pro Beat eine neue Farbe.</t>
         </is>
@@ -777,7 +777,7 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>progBlack(1905, 40)
+          <t>progBlack(1905, 10)
 Alter Effekt: 1 Takt schwarz.</t>
         </is>
       </c>
@@ -809,7 +809,7 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>progMatrixHorizontal(15238, 45, 70, true)
+          <t>progMatrixHorizontal(15238, 11, 70, true)
 Alter Effekt: Leuchtspuren laufen durch und hellen nach Weiß auf.</t>
         </is>
       </c>
@@ -841,7 +841,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>progWaterRipple(15238, 50, 50, true, true)
+          <t>progWaterRipple(15238, 12, 50, true, true)
 Alter Effekt: Wasserringe breiten sich von der Mitte aus, mit Farbverlauf.</t>
         </is>
       </c>
@@ -873,7 +873,7 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>progRandomLines(13334, 55, 476, false)
+          <t>progRandomLines(13334, 13, 476, false)
 Alter Effekt: pro Beat eine weitere zufällige Linie, die Linien bleiben stehen und füllen das Bild.</t>
         </is>
       </c>
@@ -901,7 +901,7 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>progFastBlingBling(1905, 6, 60)
+          <t>progFastBlingBling(1905, 6, 14)
 Alter Effekt: 1 Takt schnelle Einzelblitze als Auftakt zum Chorus.</t>
         </is>
       </c>
@@ -933,7 +933,7 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>progFullColors(13333, 65, 476)
+          <t>progFullColors(13333, 15, 476)
 Alter Effekt: alle LEDs einfarbig, pro Beat eine neue Farbe.</t>
         </is>
       </c>
@@ -965,7 +965,7 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>progStrobo(1905, 70, 120, 255, 255, 255)
+          <t>progStrobo(1905, 16, 120, 255, 255, 255)
 Alter Effekt: 1 Takt harter weißer Strobo (120 ms).</t>
         </is>
       </c>
@@ -997,7 +997,7 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>progFastBlingBling(15238, 2, 75, 1, 20, 952)
+          <t>progFastBlingBling(15238, 2, 17, 1, 20, 952)
 Ausgabe: Blinder bei 14762 ms, 952 ms lang, Blinder blendet 0 ms ein, 476 ms voll, 476 ms aus
 Alter Effekt: schnelle Einzelblitze, die über den Part dichter werden (alle 2 Beats eine LED mehr, bis 20). Auf dem letzten Viertel springt ein starker Blinder auf (warmweiß, alle Geräte), steht dieses Viertel voll hell und klingt danach 5 Sekunden lang ins Schluss-Schwarz aus.</t>
         </is>

--- a/songs/BeMine_v1/quelle/struktur.xlsx
+++ b/songs/BeMine_v1/quelle/struktur.xlsx
@@ -31,7 +31,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +41,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFBDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -56,7 +62,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -73,6 +79,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -438,17 +447,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -474,6 +484,7 @@
       </c>
       <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -486,6 +497,7 @@
       </c>
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -498,6 +510,7 @@
       </c>
       <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -517,25 +530,30 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>Alter Effekt (temporär)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>Änderungswunsch</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Neuer Vorschlag (KI)</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Energie 0-5</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>BPM pro Part</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>bisher (alter Code)</t>
         </is>
@@ -558,12 +576,13 @@
       </c>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>progBlack(5000, 5)   (Matrix: progScrollText("Be Mine by Kamrad", 20238, 75, getRandomColor(), 10))</t>
         </is>
@@ -585,17 +604,18 @@
         </is>
       </c>
       <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>Szene Glow, SUNSET, weich eingeblendet (fade_in 4 Beats).</t>
         </is>
       </c>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>progBlingBlingColoring(15238, 10, 946)</t>
         </is>
@@ -610,24 +630,30 @@
           <t>verse 1a</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>SCENE_VERSE_STARS, Farben SCHEME_ICE
+Strophe neu (18.10.2026, statt der alten Palette): ruhiger Einstieg als Sternenhimmel - auf jedem Beat leuchten ein paar Sterne in Blau/Weiß auf und verglimmen</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>progPalette(15238, 1, 5)
 Alter Effekt: Regenbogen-Streifen mit harten Kanten laufen über die Geräte.</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>Szene Verse, SUNSET: dezenter Puls im Beat (bisher Regenbogen-Streifen).</t>
         </is>
       </c>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>progPalette(15238, 1, 12)</t>
         </is>
@@ -642,24 +668,30 @@
           <t>verse 1b</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>SCENE_VERSE_HEART, Farben SCHEME_NEON
+Strophe neu (18.10.2026): 'be mine' - alle Geräte schlagen auf jedem Beat wie ein Herz in Pink/Cyan/Violett, die Matrix zeigt eine Lissajous-Schleife</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>progPalette(15238, 4, 6)
 Alter Effekt: bunte, unterschiedlich helle Farbflecken laufen weich über die Geräte.</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>Szene Palette, SUNSET -&gt; Farbwanderung nach NEON (2 Takte): Farbband über die ganze Bühne.</t>
         </is>
       </c>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>progPalette(15238, 4, 14)</t>
         </is>
@@ -681,17 +713,18 @@
         </is>
       </c>
       <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>Linien bleiben (stapeln sich), darüber baut sich ein Glitzern auf (Ebene Sparkle, fade_in über 7 Takte). Fester Look für beide.</t>
         </is>
       </c>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(13333, 16, 470, false)</t>
         </is>
@@ -713,17 +746,18 @@
         </is>
       </c>
       <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>Szene Buildup (1 Takt), NEON: lädt sich auf, Explosion genau auf den Chorus - der Blinder des Users steht dann auf dem Einsatz.</t>
         </is>
       </c>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(1905, 6, 18)</t>
         </is>
@@ -745,22 +779,23 @@
 Auf den Chorus-Einsatz springt ein starker Blinder auf (warmweiß, alle Geräte): 2 Beats voll hell, klingt über 2 Beats ab. Darunter der alte Effekt: alle LEDs einfarbig, pro Beat eine neue Farbe.</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>starker blinder am Anfang!</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>Szene Colors, NEON, soft 30 (feste Farben, kurze Blende); Blinder am Anfang bleibt. Auf der Matrix "BE MINE" über der Szene (2 Takte, blendet aus).</t>
         </is>
       </c>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>progFullColors(15238, 20, 470)</t>
         </is>
@@ -782,17 +817,18 @@
         </is>
       </c>
       <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>Schwarz bleibt; in den letzten 2 Beats weich ins Verse (verse 2 mit Übergang fade).</t>
         </is>
       </c>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>progBlack(1905, 22)</t>
         </is>
@@ -807,24 +843,30 @@
           <t>verse 2</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>SCENE_VERSE_WAVES, Farben SCHEME_ROYAL
+Strophe neu (18.10.2026, statt der alten Leuchtspuren): Sinuswellen laufen im Takt über die Matrix, eine Lichtebene fährt je Takt über Gitarre und Bass, Lichtschuss in den Lampen - Blau/Lila/Weiß</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>progMatrixHorizontal(15238, 11, 70, true)
 Alter Effekt: Leuchtspuren laufen durch und hellen nach Weiß auf.</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>Leuchtspuren bleiben (Szene Rain, ROYAL) - kühler Kontrast zum Chorus.</t>
         </is>
       </c>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>progMatrixHorizontal(15238, 24, 70, true)</t>
         </is>
@@ -846,17 +888,18 @@
         </is>
       </c>
       <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>Szene DNA Flip, NEON: stehende Helix auf der Matrix, alle anderen pulsieren einmal je Takt (bisher Wasserringe).</t>
         </is>
       </c>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(15238, 26, 50, true, true)</t>
         </is>
@@ -879,12 +922,13 @@
       </c>
       <c r="D16" s="6" t="n"/>
       <c r="E16" s="6" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(13333, 28, 470, false)</t>
         </is>
@@ -906,17 +950,18 @@
         </is>
       </c>
       <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>wie beim ersten Mal (Buildup).</t>
         </is>
       </c>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(1905, 6, 30)</t>
         </is>
@@ -938,17 +983,18 @@
         </is>
       </c>
       <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>Colors wie chorus 1, Blinder auf den Einsatz, Lampen blitzen weiß auf 2 und 4.</t>
         </is>
       </c>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>progFullColors(13333, 32, 474)</t>
         </is>
@@ -970,17 +1016,18 @@
         </is>
       </c>
       <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>Starker Blinder statt Strobo: blendet 2 Beats ein und steht 2 Beats voll bis zum Einsatz von chorus 3.</t>
         </is>
       </c>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1905, 34, 120, 255, 255, 255)</t>
         </is>
@@ -1002,22 +1049,23 @@
 Alter Effekt: schnelle Einzelblitze, die über den Part dichter werden (alle 2 Beats eine LED mehr, bis 20). Auf dem letzten Viertel springt ein starker Blinder auf (warmweiß, alle Geräte), steht dieses Viertel voll hell und klingt danach 5 Sekunden lang ins Schluss-Schwarz aus.</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>blinder am ende</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>Anwachsende Einzelblitze bleiben, in FIRE; drei kurze Blinder Ende des 4. Takts (Takt 80,5 / 80,75 / 81). Der Blinder am Ende bleibt.</t>
         </is>
       </c>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(15238, 2, 36, 1, 20, 946)</t>
         </is>
@@ -1037,10 +1085,10 @@
           <t>10 sek. BLACK</t>
         </is>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>0</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <f>$C$3</f>
         <v/>
       </c>
